--- a/data/asset_manifest.xlsx
+++ b/data/asset_manifest.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,10 +447,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>card_df_001</v>
+        <v>card_gk_002</v>
       </c>
       <c r="B3" t="str">
-        <v>assets/cards/card_df_001.png</v>
+        <v>assets/cards/card_gk_002.png</v>
       </c>
       <c r="C3">
         <v>256</v>
@@ -465,15 +465,15 @@
         <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>后卫001卡面</v>
+        <v>守门员002卡面</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>card_df_002</v>
+        <v>card_df_001</v>
       </c>
       <c r="B4" t="str">
-        <v>assets/cards/card_df_002.png</v>
+        <v>assets/cards/card_df_001.png</v>
       </c>
       <c r="C4">
         <v>256</v>
@@ -488,15 +488,15 @@
         <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>后卫002卡面</v>
+        <v>后卫001卡面</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>card_mf_001</v>
+        <v>card_df_002</v>
       </c>
       <c r="B5" t="str">
-        <v>assets/cards/card_mf_001.png</v>
+        <v>assets/cards/card_df_002.png</v>
       </c>
       <c r="C5">
         <v>256</v>
@@ -511,15 +511,15 @@
         <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>中场001卡面</v>
+        <v>后卫002卡面</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>card_mf_002</v>
+        <v>card_df_003</v>
       </c>
       <c r="B6" t="str">
-        <v>assets/cards/card_mf_002.png</v>
+        <v>assets/cards/card_df_003.png</v>
       </c>
       <c r="C6">
         <v>256</v>
@@ -534,15 +534,15 @@
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>中场002卡面</v>
+        <v>后卫003卡面</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>card_fw_001</v>
+        <v>card_mf_001</v>
       </c>
       <c r="B7" t="str">
-        <v>assets/cards/card_fw_001.png</v>
+        <v>assets/cards/card_mf_001.png</v>
       </c>
       <c r="C7">
         <v>256</v>
@@ -557,15 +557,15 @@
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>前锋001卡面</v>
+        <v>中场001卡面</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>card_fw_002</v>
+        <v>card_mf_002</v>
       </c>
       <c r="B8" t="str">
-        <v>assets/cards/card_fw_002.png</v>
+        <v>assets/cards/card_mf_002.png</v>
       </c>
       <c r="C8">
         <v>256</v>
@@ -580,15 +580,15 @@
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>前锋002卡面</v>
+        <v>中场002卡面</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>card_fw_003</v>
+        <v>card_mf_003</v>
       </c>
       <c r="B9" t="str">
-        <v>assets/cards/card_fw_003.png</v>
+        <v>assets/cards/card_mf_003.png</v>
       </c>
       <c r="C9">
         <v>256</v>
@@ -603,81 +603,219 @@
         <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>前锋003卡面</v>
+        <v>中场003卡面</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>pitch_bg</v>
+        <v>card_mf_004</v>
       </c>
       <c r="B10" t="str">
-        <v>assets/pitch/pitch_bg.png</v>
+        <v>assets/cards/card_mf_004.png</v>
       </c>
       <c r="C10">
-        <v>1136</v>
+        <v>256</v>
       </c>
       <c r="D10">
-        <v>640</v>
+        <v>360</v>
       </c>
       <c r="E10" t="str">
-        <v>pitch</v>
+        <v>card</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>球场全景背景</v>
+        <v>中场004卡面</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>btn_primary</v>
+        <v>card_fw_001</v>
       </c>
       <c r="B11" t="str">
-        <v>assets/ui/btn_primary.png</v>
+        <v>assets/cards/card_fw_001.png</v>
       </c>
       <c r="C11">
-        <v>200</v>
+        <v>256</v>
       </c>
       <c r="D11">
-        <v>56</v>
+        <v>360</v>
       </c>
       <c r="E11" t="str">
-        <v>ui</v>
+        <v>card</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>主按钮</v>
+        <v>前锋001卡面</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>card_fw_002</v>
+      </c>
+      <c r="B12" t="str">
+        <v>assets/cards/card_fw_002.png</v>
+      </c>
+      <c r="C12">
+        <v>256</v>
+      </c>
+      <c r="D12">
+        <v>360</v>
+      </c>
+      <c r="E12" t="str">
+        <v>card</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <v>前锋002卡面</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>card_fw_003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>assets/cards/card_fw_003.png</v>
+      </c>
+      <c r="C13">
+        <v>256</v>
+      </c>
+      <c r="D13">
+        <v>360</v>
+      </c>
+      <c r="E13" t="str">
+        <v>card</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <v>前锋003卡面</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>card_fw_004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>assets/cards/card_fw_004.png</v>
+      </c>
+      <c r="C14">
+        <v>256</v>
+      </c>
+      <c r="D14">
+        <v>360</v>
+      </c>
+      <c r="E14" t="str">
+        <v>card</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <v>前锋004卡面</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>card_fw_005</v>
+      </c>
+      <c r="B15" t="str">
+        <v>assets/cards/card_fw_005.png</v>
+      </c>
+      <c r="C15">
+        <v>256</v>
+      </c>
+      <c r="D15">
+        <v>360</v>
+      </c>
+      <c r="E15" t="str">
+        <v>card</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <v>前锋005卡面</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>pitch_bg</v>
+      </c>
+      <c r="B16" t="str">
+        <v>assets/pitch/pitch_bg.png</v>
+      </c>
+      <c r="C16">
+        <v>1136</v>
+      </c>
+      <c r="D16">
+        <v>640</v>
+      </c>
+      <c r="E16" t="str">
+        <v>pitch</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="str">
+        <v>球场全景背景</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>btn_primary</v>
+      </c>
+      <c r="B17" t="str">
+        <v>assets/ui/btn_primary.png</v>
+      </c>
+      <c r="C17">
+        <v>200</v>
+      </c>
+      <c r="D17">
+        <v>56</v>
+      </c>
+      <c r="E17" t="str">
+        <v>ui</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="str">
+        <v>主按钮</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>logo</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B18" t="str">
         <v>assets/ui/logo.png</v>
       </c>
-      <c r="C12">
+      <c r="C18">
         <v>512</v>
       </c>
-      <c r="D12">
-        <v>256</v>
-      </c>
-      <c r="E12" t="str">
+      <c r="D18">
+        <v>256</v>
+      </c>
+      <c r="E18" t="str">
         <v>ui</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="str">
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="str">
         <v>游戏Logo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G18"/>
   </ignoredErrors>
 </worksheet>
 </file>